--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/OREGON_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/OREGON_2013.xlsx
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C73">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C197">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C710">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C711">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C750">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1164">
